--- a/data/trans_dic/IP1009-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1009-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen transtornos intestinales crónicos</t>
+          <t>Menores que padecen transtornos intestinales crónicos (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>0,0; 1,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,94</t>
+          <t>0,0; 1,09</t>
         </is>
       </c>
     </row>
@@ -792,42 +793,42 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,21</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 2,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,96</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,3</t>
+          <t>0,15; 1,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,05</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,01</t>
+          <t>0,0; 1,14</t>
         </is>
       </c>
     </row>
@@ -897,12 +898,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -912,32 +913,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,5</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,0; 0,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,58</t>
+          <t>0,14; 1,53</t>
         </is>
       </c>
     </row>
@@ -1007,32 +1008,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,21</t>
+          <t>0,0; 2,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,35</t>
+          <t>0,0; 2,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1042,7 +1043,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,86</t>
+          <t>0,0; 0,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1122,12 +1123,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,64</t>
+          <t>0,0; 0,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,93</t>
+          <t>0,11; 1,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1137,27 +1138,27 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,43</t>
+          <t>0,0; 0,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,93</t>
+          <t>0,09; 0,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,47</t>
+          <t>0,08; 0,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,36</t>
+          <t>0,0; 0,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,74</t>
+          <t>0,19; 0,72</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen transtornos intestinales crónicos (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2582</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3082</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1377</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1452</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1452</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3176</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3941</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4827</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4384</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>631; 5800</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3996</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4924</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1251</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1706</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2159</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2313</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4329</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2253</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>452; 4932</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1525</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1525</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5264</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4681</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3105</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3478</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3125</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5377</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2585</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2072</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2702</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3153</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1922</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>5287</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3703</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5022</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>769; 7162</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>676; 5558</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3116</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>674; 6732</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1134; 7238</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4520</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>2681; 10498</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1009-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1009-Habitat-trans_dic.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,93</t>
+          <t>0,0; 2,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,09</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 2,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,28</t>
+          <t>0,0; 2,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>0,0; 2,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,42</t>
+          <t>0,0; 1,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,14</t>
+          <t>0,0; 1,02</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 1,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 2,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,53</t>
+          <t>0,14; 1,41</t>
         </is>
       </c>
     </row>
@@ -1018,17 +1018,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,54</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,25</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,5</t>
+          <t>0,0; 1,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,83</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,75</t>
+          <t>0,0; 0,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1118,17 +1118,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,54</t>
+          <t>0,0; 0,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,71</t>
+          <t>0,0; 0,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,02</t>
+          <t>0,09; 0,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1138,27 +1138,27 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,42</t>
+          <t>0,0; 0,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,9</t>
+          <t>0,09; 0,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,52</t>
+          <t>0,08; 0,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,31</t>
+          <t>0,04; 0,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,72</t>
+          <t>0,18; 0,72</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2582</t>
+          <t>0; 3607</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3082</t>
+          <t>0; 3367</t>
         </is>
       </c>
     </row>
@@ -1580,12 +1580,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3176</t>
+          <t>0; 3179</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3941</t>
+          <t>0; 5138</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4827</t>
+          <t>0; 4815</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1605,22 +1605,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4384</t>
+          <t>0; 4644</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>631; 5800</t>
+          <t>0; 5773</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3996</t>
+          <t>0; 3962</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4924</t>
+          <t>0; 4409</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2159</t>
+          <t>0; 1820</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2313</t>
+          <t>0; 2304</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4329</t>
+          <t>0; 4717</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>452; 4932</t>
+          <t>455; 4553</t>
         </is>
       </c>
     </row>
@@ -1916,17 +1916,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5264</t>
+          <t>0; 5398</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4681</t>
+          <t>0; 3999</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3105</t>
+          <t>0; 3727</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1936,17 +1936,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3478</t>
+          <t>0; 3948</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3125</t>
+          <t>0; 3710</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5377</t>
+          <t>0; 5360</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3703</t>
+          <t>0; 4250</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5022</t>
+          <t>0; 4580</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>769; 7162</t>
+          <t>606; 6369</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>676; 5558</t>
+          <t>677; 5551</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3116</t>
+          <t>0; 3462</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>674; 6732</t>
+          <t>668; 6869</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1134; 7238</t>
+          <t>1085; 7090</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 4520</t>
+          <t>617; 4572</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2681; 10498</t>
+          <t>2566; 10422</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1009-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1009-Habitat-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -635,22 +635,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>0,45%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,63%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 1,96</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>0,0; 1,63</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,5</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,27</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,16; 1,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,93</t>
+          <t>0,0; 1,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,02</t>
+          <t>0,0; 1,01</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -908,27 +908,27 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,5</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 1,63</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 1,48</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,83</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,78</t>
+          <t>0,0; 0,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,41</t>
+          <t>0,14; 1,58</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,74%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,42 +1008,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,8</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 0,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,89</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,16%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,18%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0,37%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,62</t>
+          <t>0,09; 0,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,65</t>
+          <t>0,0; 0,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,9</t>
+          <t>0,1; 0,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,77</t>
+          <t>0,0; 0,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,46</t>
+          <t>0,0; 0,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,92</t>
+          <t>0,11; 0,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,51</t>
+          <t>0,08; 0,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,31</t>
+          <t>0,04; 0,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,72</t>
+          <t>0,17; 0,74</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1321,22 +1321,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1374,22 +1374,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>605</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3607</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3017</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3367</t>
+          <t>0; 2641</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1377</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1452</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>634</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1303</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1377</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1452</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3179</t>
+          <t>0; 4585</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5138</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4398</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4815</t>
+          <t>0; 3174</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4548</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4644</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5773</t>
+          <t>632; 5314</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3962</t>
+          <t>0; 4498</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4409</t>
+          <t>0; 4349</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1251</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>448</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>455</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1251</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1820</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2304</t>
+          <t>0; 4160</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2242</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4717</t>
+          <t>0; 2311</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2253</t>
+          <t>0; 2419</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>455; 4553</t>
+          <t>454; 5111</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>695</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>619</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>1525</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2797</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3487</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5398</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3999</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3727</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4587</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3948</t>
+          <t>0; 3478</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3710</t>
+          <t>0; 3580</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5360</t>
+          <t>0; 5355</t>
         </is>
       </c>
     </row>
@@ -1963,27 +1963,27 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2072</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2702</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>1081</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1303</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>2585</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2072</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2702</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4250</t>
+          <t>679; 5550</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4580</t>
+          <t>0; 3197</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>606; 6369</t>
+          <t>716; 6921</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>677; 5551</t>
+          <t>0; 3695</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3462</t>
+          <t>0; 4504</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>668; 6869</t>
+          <t>754; 6577</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1085; 7090</t>
+          <t>1082; 6622</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>617; 4572</t>
+          <t>619; 5193</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2566; 10422</t>
+          <t>2472; 10690</t>
         </is>
       </c>
     </row>
